--- a/artfynd/A 23329-2025 artfynd.xlsx
+++ b/artfynd/A 23329-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126270163</v>
       </c>
       <c r="B2" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>126270179</v>
       </c>
       <c r="B3" t="n">
-        <v>92528</v>
+        <v>92532</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 23329-2025 artfynd.xlsx
+++ b/artfynd/A 23329-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126270163</v>
       </c>
       <c r="B2" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>126270179</v>
       </c>
       <c r="B3" t="n">
-        <v>92532</v>
+        <v>92535</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
